--- a/benchmarks/attachment_intelligence/fixtures/files/f40.xlsx
+++ b/benchmarks/attachment_intelligence/fixtures/files/f40.xlsx
@@ -67,7 +67,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цена, руб.</t>
+          <t xml:space="preserve">Цена за 100 шт., руб.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
